--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/118.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/118.xlsx
@@ -426,13 +426,13 @@
         <v>-8.606914472607032</v>
       </c>
       <c r="E2">
-        <v>-30.37439279065793</v>
+        <v>-28.63736978774375</v>
       </c>
       <c r="F2">
-        <v>-4.210530356489588</v>
+        <v>-4.016390030132482</v>
       </c>
       <c r="G2">
-        <v>-18.59294357560247</v>
+        <v>-17.54001794574619</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.766454445783605</v>
       </c>
       <c r="E3">
-        <v>-30.39233460467632</v>
+        <v>-28.91618340392201</v>
       </c>
       <c r="F3">
-        <v>-3.978835993926566</v>
+        <v>-3.850212902191678</v>
       </c>
       <c r="G3">
-        <v>-18.20882594249914</v>
+        <v>-17.48351189920914</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.860025145118062</v>
       </c>
       <c r="E4">
-        <v>-31.08827501864911</v>
+        <v>-29.01211912577451</v>
       </c>
       <c r="F4">
-        <v>-4.02127491270679</v>
+        <v>-3.804901205258545</v>
       </c>
       <c r="G4">
-        <v>-18.28250544402116</v>
+        <v>-16.83640452846611</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.860801646119098</v>
       </c>
       <c r="E5">
-        <v>-31.04829312163539</v>
+        <v>-29.57719343363663</v>
       </c>
       <c r="F5">
-        <v>-3.993873347389585</v>
+        <v>-3.791378935775246</v>
       </c>
       <c r="G5">
-        <v>-18.22677903095861</v>
+        <v>-17.33412353174953</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.758842860765895</v>
       </c>
       <c r="E6">
-        <v>-30.9053654250053</v>
+        <v>-29.16328864509856</v>
       </c>
       <c r="F6">
-        <v>-4.087149173679615</v>
+        <v>-3.695134240713583</v>
       </c>
       <c r="G6">
-        <v>-18.28617021793313</v>
+        <v>-17.07003303771802</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.549971277840724</v>
       </c>
       <c r="E7">
-        <v>-31.56058580070112</v>
+        <v>-29.81998756755788</v>
       </c>
       <c r="F7">
-        <v>-4.005006605283211</v>
+        <v>-3.738982212445969</v>
       </c>
       <c r="G7">
-        <v>-18.18577957972751</v>
+        <v>-17.45820112328864</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.231697655470438</v>
       </c>
       <c r="E8">
-        <v>-31.66462749102734</v>
+        <v>-30.43197686613947</v>
       </c>
       <c r="F8">
-        <v>-4.069164488997435</v>
+        <v>-3.791115514941156</v>
       </c>
       <c r="G8">
-        <v>-17.98120938394655</v>
+        <v>-16.87279570030655</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.798511352217846</v>
       </c>
       <c r="E9">
-        <v>-32.37461975984593</v>
+        <v>-30.45270369167258</v>
       </c>
       <c r="F9">
-        <v>-3.829092846889902</v>
+        <v>-3.635761835485331</v>
       </c>
       <c r="G9">
-        <v>-18.30469934131644</v>
+        <v>-17.00488977786901</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.255867455326802</v>
       </c>
       <c r="E10">
-        <v>-32.74751468777054</v>
+        <v>-31.25262919004649</v>
       </c>
       <c r="F10">
-        <v>-4.095662305478186</v>
+        <v>-3.807727594836897</v>
       </c>
       <c r="G10">
-        <v>-18.00977939195046</v>
+        <v>-17.10562636808349</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.615675658449242</v>
       </c>
       <c r="E11">
-        <v>-33.16030094322872</v>
+        <v>-31.26513230678167</v>
       </c>
       <c r="F11">
-        <v>-3.904222456854206</v>
+        <v>-3.658831867653297</v>
       </c>
       <c r="G11">
-        <v>-17.42171063508203</v>
+        <v>-16.306909253824</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.893576028861877</v>
       </c>
       <c r="E12">
-        <v>-33.6903361834565</v>
+        <v>-32.32657717909856</v>
       </c>
       <c r="F12">
-        <v>-3.780445314425696</v>
+        <v>-3.557325382849052</v>
       </c>
       <c r="G12">
-        <v>-17.36474773326055</v>
+        <v>-16.5612203963325</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.108163980274481</v>
       </c>
       <c r="E13">
-        <v>-33.98850449754354</v>
+        <v>-32.55225368127081</v>
       </c>
       <c r="F13">
-        <v>-3.772017504469613</v>
+        <v>-3.459337802771898</v>
       </c>
       <c r="G13">
-        <v>-17.38147095405218</v>
+        <v>-16.44480837298957</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.295984181460517</v>
       </c>
       <c r="E14">
-        <v>-34.80320414236748</v>
+        <v>-33.1124666722857</v>
       </c>
       <c r="F14">
-        <v>-3.60132494581615</v>
+        <v>-3.444213470731585</v>
       </c>
       <c r="G14">
-        <v>-16.85942771741897</v>
+        <v>-16.05086338545291</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.488075514100586</v>
       </c>
       <c r="E15">
-        <v>-35.55220242205114</v>
+        <v>-33.31549174747158</v>
       </c>
       <c r="F15">
-        <v>-3.503242103487675</v>
+        <v>-3.41712254319043</v>
       </c>
       <c r="G15">
-        <v>-16.55630092566114</v>
+        <v>-15.84000811896565</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.712479278639982</v>
       </c>
       <c r="E16">
-        <v>-35.7457109091099</v>
+        <v>-34.42548865386171</v>
       </c>
       <c r="F16">
-        <v>-3.345897857162922</v>
+        <v>-3.197281289794066</v>
       </c>
       <c r="G16">
-        <v>-16.50301769520657</v>
+        <v>-15.60901645923578</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.999968262094476</v>
       </c>
       <c r="E17">
-        <v>-36.71579608255905</v>
+        <v>-35.22170759626034</v>
       </c>
       <c r="F17">
-        <v>-3.362336808271479</v>
+        <v>-2.987134420112665</v>
       </c>
       <c r="G17">
-        <v>-15.87925132578818</v>
+        <v>-15.58995268274788</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.375348534289857</v>
       </c>
       <c r="E18">
-        <v>-37.29006092841973</v>
+        <v>-35.53395267180023</v>
       </c>
       <c r="F18">
-        <v>-3.0567694690942</v>
+        <v>-2.703089722794923</v>
       </c>
       <c r="G18">
-        <v>-15.80451244969359</v>
+        <v>-15.01329372108054</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.8523360921268227</v>
       </c>
       <c r="E19">
-        <v>-38.27687654909021</v>
+        <v>-36.3551642622472</v>
       </c>
       <c r="F19">
-        <v>-2.996866080360753</v>
+        <v>-2.551051169685102</v>
       </c>
       <c r="G19">
-        <v>-15.55707399972461</v>
+        <v>-14.46912445333561</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.4348824506092149</v>
       </c>
       <c r="E20">
-        <v>-38.47722756037457</v>
+        <v>-37.46973945585908</v>
       </c>
       <c r="F20">
-        <v>-2.965953065623081</v>
+        <v>-2.680785102107143</v>
       </c>
       <c r="G20">
-        <v>-15.45951222268229</v>
+        <v>-14.16226005566395</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.1288122543896762</v>
       </c>
       <c r="E21">
-        <v>-39.0255374574603</v>
+        <v>-37.6315780599452</v>
       </c>
       <c r="F21">
-        <v>-2.630470894428504</v>
+        <v>-2.382241490138202</v>
       </c>
       <c r="G21">
-        <v>-15.39776558255657</v>
+        <v>-14.53375457862603</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.07243286208482347</v>
       </c>
       <c r="E22">
-        <v>-39.23994938053847</v>
+        <v>-37.81048674680324</v>
       </c>
       <c r="F22">
-        <v>-2.387369084361531</v>
+        <v>-2.374676839015836</v>
       </c>
       <c r="G22">
-        <v>-14.84628166444262</v>
+        <v>-14.16057995380277</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.1808178037144856</v>
       </c>
       <c r="E23">
-        <v>-39.43576059663013</v>
+        <v>-38.42073484712888</v>
       </c>
       <c r="F23">
-        <v>-2.474826458014297</v>
+        <v>-2.386476932668716</v>
       </c>
       <c r="G23">
-        <v>-14.7453563731324</v>
+        <v>-13.59007033047462</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.2068617378382208</v>
       </c>
       <c r="E24">
-        <v>-39.84837477007602</v>
+        <v>-38.88319166974019</v>
       </c>
       <c r="F24">
-        <v>-2.499805048678313</v>
+        <v>-2.163978276644171</v>
       </c>
       <c r="G24">
-        <v>-14.9426681978185</v>
+        <v>-13.21698012456261</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.1618066519190932</v>
       </c>
       <c r="E25">
-        <v>-40.42410910575221</v>
+        <v>-39.32572320671775</v>
       </c>
       <c r="F25">
-        <v>-2.265498015326862</v>
+        <v>-2.205181271259419</v>
       </c>
       <c r="G25">
-        <v>-14.80152805456998</v>
+        <v>-13.84648697994611</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.05704515033622228</v>
       </c>
       <c r="E26">
-        <v>-40.7252028140482</v>
+        <v>-39.20106790270861</v>
       </c>
       <c r="F26">
-        <v>-1.990687129448126</v>
+        <v>-1.933003765354182</v>
       </c>
       <c r="G26">
-        <v>-14.72914297635382</v>
+        <v>-13.43353946101404</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.09720165302915215</v>
       </c>
       <c r="E27">
-        <v>-40.74174080112422</v>
+        <v>-39.05029462486023</v>
       </c>
       <c r="F27">
-        <v>-2.122921903059219</v>
+        <v>-2.132117609597696</v>
       </c>
       <c r="G27">
-        <v>-14.45539065516595</v>
+        <v>-13.994845767743</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.293123488037396</v>
       </c>
       <c r="E28">
-        <v>-40.6705939459897</v>
+        <v>-39.6656916001326</v>
       </c>
       <c r="F28">
-        <v>-2.293651738245809</v>
+        <v>-2.040254978096843</v>
       </c>
       <c r="G28">
-        <v>-14.67845521360204</v>
+        <v>-13.97966691644545</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.5258909536098526</v>
       </c>
       <c r="E29">
-        <v>-40.81323408452031</v>
+        <v>-39.26475636115249</v>
       </c>
       <c r="F29">
-        <v>-2.21544640011491</v>
+        <v>-2.022681163646451</v>
       </c>
       <c r="G29">
-        <v>-14.70126652764039</v>
+        <v>-13.60111265512086</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.7913188682701958</v>
       </c>
       <c r="E30">
-        <v>-40.59994522299604</v>
+        <v>-39.78049520893805</v>
       </c>
       <c r="F30">
-        <v>-2.274339180616941</v>
+        <v>-1.892080758921081</v>
       </c>
       <c r="G30">
-        <v>-15.17471426630264</v>
+        <v>-13.78043828589211</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.084228525653339</v>
       </c>
       <c r="E31">
-        <v>-40.29780543720427</v>
+        <v>-39.13277398619893</v>
       </c>
       <c r="F31">
-        <v>-2.190598691500536</v>
+        <v>-2.154167093125414</v>
       </c>
       <c r="G31">
-        <v>-14.78092156386079</v>
+        <v>-14.15315605543095</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.401380647914033</v>
       </c>
       <c r="E32">
-        <v>-39.90855592540096</v>
+        <v>-38.47992426664614</v>
       </c>
       <c r="F32">
-        <v>-2.103232438262078</v>
+        <v>-2.234677777738303</v>
       </c>
       <c r="G32">
-        <v>-15.07137889783983</v>
+        <v>-13.96342703530255</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.74061659253444</v>
       </c>
       <c r="E33">
-        <v>-39.94508938945784</v>
+        <v>-38.88419925520689</v>
       </c>
       <c r="F33">
-        <v>-2.290200759645746</v>
+        <v>-2.272863029905152</v>
       </c>
       <c r="G33">
-        <v>-15.21297093055446</v>
+        <v>-14.07341494502653</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.097755033540242</v>
       </c>
       <c r="E34">
-        <v>-39.87306853883985</v>
+        <v>-38.27869699564129</v>
       </c>
       <c r="F34">
-        <v>-2.26344697763753</v>
+        <v>-2.096829158238438</v>
       </c>
       <c r="G34">
-        <v>-15.13057807317307</v>
+        <v>-14.03786630702583</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.464964767842047</v>
       </c>
       <c r="E35">
-        <v>-39.0088930512451</v>
+        <v>-37.92290384980665</v>
       </c>
       <c r="F35">
-        <v>-2.14018176626395</v>
+        <v>-1.974543077134966</v>
       </c>
       <c r="G35">
-        <v>-15.48920450562401</v>
+        <v>-13.95634743366682</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.841302274238028</v>
       </c>
       <c r="E36">
-        <v>-38.81803598571783</v>
+        <v>-37.94303065253374</v>
       </c>
       <c r="F36">
-        <v>-2.300334178084192</v>
+        <v>-2.075937732339834</v>
       </c>
       <c r="G36">
-        <v>-15.18235666068004</v>
+        <v>-14.02962635917859</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.224554558391302</v>
       </c>
       <c r="E37">
-        <v>-38.79632195285105</v>
+        <v>-37.04253680339747</v>
       </c>
       <c r="F37">
-        <v>-2.280254552240332</v>
+        <v>-1.854133248198836</v>
       </c>
       <c r="G37">
-        <v>-15.41595206447656</v>
+        <v>-14.57202614033278</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.607924667745859</v>
       </c>
       <c r="E38">
-        <v>-38.11067023182369</v>
+        <v>-36.51787459757981</v>
       </c>
       <c r="F38">
-        <v>-2.292332977340552</v>
+        <v>-2.059052291201169</v>
       </c>
       <c r="G38">
-        <v>-15.51603813249258</v>
+        <v>-14.50670576629742</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.987877678033709</v>
       </c>
       <c r="E39">
-        <v>-37.6741457156173</v>
+        <v>-35.88054622268829</v>
       </c>
       <c r="F39">
-        <v>-2.253413791654822</v>
+        <v>-1.96894579859425</v>
       </c>
       <c r="G39">
-        <v>-15.46244371075731</v>
+        <v>-14.54322439414112</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.361489644560988</v>
       </c>
       <c r="E40">
-        <v>-37.23043903963475</v>
+        <v>-36.17655445467367</v>
       </c>
       <c r="F40">
-        <v>-2.261998991417437</v>
+        <v>-1.943058488889363</v>
       </c>
       <c r="G40">
-        <v>-15.59311094319235</v>
+        <v>-14.32868449046865</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.722291340148046</v>
       </c>
       <c r="E41">
-        <v>-37.00661468333163</v>
+        <v>-35.64879703687176</v>
       </c>
       <c r="F41">
-        <v>-2.235966717417059</v>
+        <v>-1.924750740920091</v>
       </c>
       <c r="G41">
-        <v>-15.37265840518674</v>
+        <v>-14.15603954059566</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.060959438582651</v>
       </c>
       <c r="E42">
-        <v>-36.0354698469647</v>
+        <v>-34.74485701901565</v>
       </c>
       <c r="F42">
-        <v>-2.248776590933951</v>
+        <v>-1.829877822277463</v>
       </c>
       <c r="G42">
-        <v>-15.69517506216808</v>
+        <v>-14.07619580327952</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.376207466573534</v>
       </c>
       <c r="E43">
-        <v>-36.48858216346119</v>
+        <v>-34.08315413277786</v>
       </c>
       <c r="F43">
-        <v>-2.134282961988614</v>
+        <v>-1.594256998225172</v>
       </c>
       <c r="G43">
-        <v>-15.25884516009214</v>
+        <v>-14.11673343340789</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.665267536962268</v>
       </c>
       <c r="E44">
-        <v>-35.54701731931236</v>
+        <v>-33.9038809037622</v>
       </c>
       <c r="F44">
-        <v>-2.131131024020962</v>
+        <v>-1.759791313061403</v>
       </c>
       <c r="G44">
-        <v>-15.48893469616256</v>
+        <v>-14.40407554403447</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.923630576353472</v>
       </c>
       <c r="E45">
-        <v>-35.53458212968729</v>
+        <v>-33.27716274347066</v>
       </c>
       <c r="F45">
-        <v>-1.949358222987653</v>
+        <v>-1.916440559135206</v>
       </c>
       <c r="G45">
-        <v>-15.7097017359944</v>
+        <v>-14.17231749301225</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.153528287939977</v>
       </c>
       <c r="E46">
-        <v>-34.54533019000069</v>
+        <v>-33.08964769176105</v>
       </c>
       <c r="F46">
-        <v>-2.020196889805455</v>
+        <v>-1.643716330744122</v>
       </c>
       <c r="G46">
-        <v>-15.3241109101261</v>
+        <v>-14.55940799600985</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.359447359820394</v>
       </c>
       <c r="E47">
-        <v>-34.0210710183697</v>
+        <v>-32.78233186017852</v>
       </c>
       <c r="F47">
-        <v>-1.967588932788464</v>
+        <v>-1.726094983850324</v>
       </c>
       <c r="G47">
-        <v>-15.69547797708492</v>
+        <v>-14.53855983547629</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.544005630020654</v>
       </c>
       <c r="E48">
-        <v>-33.34139461879546</v>
+        <v>-32.68172501738711</v>
       </c>
       <c r="F48">
-        <v>-1.816918842628068</v>
+        <v>-1.709562427225252</v>
       </c>
       <c r="G48">
-        <v>-15.46483557990944</v>
+        <v>-14.40655845318893</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.710339970113465</v>
       </c>
       <c r="E49">
-        <v>-33.27300786856863</v>
+        <v>-31.71288743852708</v>
       </c>
       <c r="F49">
-        <v>-1.847778841851961</v>
+        <v>-1.601523437082529</v>
       </c>
       <c r="G49">
-        <v>-15.47177448335975</v>
+        <v>-14.45975892000501</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.868121815791755</v>
       </c>
       <c r="E50">
-        <v>-32.78636899475635</v>
+        <v>-30.8576647440455</v>
       </c>
       <c r="F50">
-        <v>-1.903890792982794</v>
+        <v>-1.730200372698599</v>
       </c>
       <c r="G50">
-        <v>-15.29965425495473</v>
+        <v>-14.29607065108852</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.022383225849191</v>
       </c>
       <c r="E51">
-        <v>-32.23629752128164</v>
+        <v>-31.27652368314797</v>
       </c>
       <c r="F51">
-        <v>-2.027932184612797</v>
+        <v>-1.582212536188467</v>
       </c>
       <c r="G51">
-        <v>-15.4348933507795</v>
+        <v>-14.46426126193842</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.174921083734351</v>
       </c>
       <c r="E52">
-        <v>-32.21012520575431</v>
+        <v>-29.80593344847507</v>
       </c>
       <c r="F52">
-        <v>-1.739724941095987</v>
+        <v>-1.392077366223897</v>
       </c>
       <c r="G52">
-        <v>-15.36503587408257</v>
+        <v>-14.44555999018708</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.331678496389245</v>
       </c>
       <c r="E53">
-        <v>-31.52368553024961</v>
+        <v>-29.7898324591408</v>
       </c>
       <c r="F53">
-        <v>-1.822438254632921</v>
+        <v>-1.635113735266049</v>
       </c>
       <c r="G53">
-        <v>-15.49619472253018</v>
+        <v>-14.24600030507981</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.496016260187476</v>
       </c>
       <c r="E54">
-        <v>-30.9723166489717</v>
+        <v>-29.6277674313543</v>
       </c>
       <c r="F54">
-        <v>-1.984803235786041</v>
+        <v>-1.284264520382138</v>
       </c>
       <c r="G54">
-        <v>-15.57974958139585</v>
+        <v>-14.44980079902289</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.666349357532797</v>
       </c>
       <c r="E55">
-        <v>-30.87749266748809</v>
+        <v>-29.11402790484312</v>
       </c>
       <c r="F55">
-        <v>-1.870018849882322</v>
+        <v>-1.649751815640919</v>
       </c>
       <c r="G55">
-        <v>-15.69205983881562</v>
+        <v>-14.68451516721167</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.840869892502307</v>
       </c>
       <c r="E56">
-        <v>-30.46090475810047</v>
+        <v>-28.90204097959606</v>
       </c>
       <c r="F56">
-        <v>-1.91760772880575</v>
+        <v>-1.564642035207687</v>
       </c>
       <c r="G56">
-        <v>-15.72465215964975</v>
+        <v>-14.29006366620751</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.021933751451488</v>
       </c>
       <c r="E57">
-        <v>-29.88575685980828</v>
+        <v>-28.95121115037134</v>
       </c>
       <c r="F57">
-        <v>-1.897660641746338</v>
+        <v>-1.32920593708622</v>
       </c>
       <c r="G57">
-        <v>-15.74637595947845</v>
+        <v>-14.77437827060242</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.205773989741624</v>
       </c>
       <c r="E58">
-        <v>-29.5587557517144</v>
+        <v>-28.16749079623387</v>
       </c>
       <c r="F58">
-        <v>-2.071438040607827</v>
+        <v>-1.569594015541622</v>
       </c>
       <c r="G58">
-        <v>-16.06842748481152</v>
+        <v>-15.05402667339574</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.387447475163562</v>
       </c>
       <c r="E59">
-        <v>-29.36042670407447</v>
+        <v>-27.8516523765689</v>
       </c>
       <c r="F59">
-        <v>-2.014737948621006</v>
+        <v>-1.76915849165226</v>
       </c>
       <c r="G59">
-        <v>-16.10092876564331</v>
+        <v>-14.67917194671129</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.567482282460205</v>
       </c>
       <c r="E60">
-        <v>-29.1849800355953</v>
+        <v>-27.10787769165309</v>
       </c>
       <c r="F60">
-        <v>-2.11184663088379</v>
+        <v>-1.856825442257934</v>
       </c>
       <c r="G60">
-        <v>-15.93646913961617</v>
+        <v>-15.40305914487387</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.743921558763899</v>
       </c>
       <c r="E61">
-        <v>-29.10760652870025</v>
+        <v>-27.2097230720856</v>
       </c>
       <c r="F61">
-        <v>-1.998549164468096</v>
+        <v>-1.763868537417982</v>
       </c>
       <c r="G61">
-        <v>-15.987688244927</v>
+        <v>-14.97911233838757</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.911897935551087</v>
       </c>
       <c r="E62">
-        <v>-28.78108091037717</v>
+        <v>-27.21311489911734</v>
       </c>
       <c r="F62">
-        <v>-2.181353282917891</v>
+        <v>-1.927770968470698</v>
       </c>
       <c r="G62">
-        <v>-16.07633637810484</v>
+        <v>-15.23227141104841</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.0688492271155</v>
       </c>
       <c r="E63">
-        <v>-28.43331674895813</v>
+        <v>-27.06471680588598</v>
       </c>
       <c r="F63">
-        <v>-2.314509201080897</v>
+        <v>-2.016631596503806</v>
       </c>
       <c r="G63">
-        <v>-16.15706899689827</v>
+        <v>-15.3547036614545</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.216343775825862</v>
       </c>
       <c r="E64">
-        <v>-28.37489943425918</v>
+        <v>-26.27912619198334</v>
       </c>
       <c r="F64">
-        <v>-2.254792195013081</v>
+        <v>-1.906611151533587</v>
       </c>
       <c r="G64">
-        <v>-16.34068178414287</v>
+        <v>-15.27052476475468</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.349708642241174</v>
       </c>
       <c r="E65">
-        <v>-28.35742858153759</v>
+        <v>-26.8005301607525</v>
       </c>
       <c r="F65">
-        <v>-2.303659244839029</v>
+        <v>-2.033049838427293</v>
       </c>
       <c r="G65">
-        <v>-16.09596625787994</v>
+        <v>-15.50392484636438</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.464693123009566</v>
       </c>
       <c r="E66">
-        <v>-27.86591254121905</v>
+        <v>-26.03087977535687</v>
       </c>
       <c r="F66">
-        <v>-2.400424154629651</v>
+        <v>-2.162695135537235</v>
       </c>
       <c r="G66">
-        <v>-16.31209025759296</v>
+        <v>-15.31489766189031</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.562597593828899</v>
       </c>
       <c r="E67">
-        <v>-28.10337666123327</v>
+        <v>-26.59540387362706</v>
       </c>
       <c r="F67">
-        <v>-2.59506232979584</v>
+        <v>-2.191663971980536</v>
       </c>
       <c r="G67">
-        <v>-16.32783190163219</v>
+        <v>-15.07101804837605</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.640898920614772</v>
       </c>
       <c r="E68">
-        <v>-27.97318756198676</v>
+        <v>-26.53468156565821</v>
       </c>
       <c r="F68">
-        <v>-2.557569592777731</v>
+        <v>-2.289456057350629</v>
       </c>
       <c r="G68">
-        <v>-16.25228525242602</v>
+        <v>-15.67470595909876</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.694782624486757</v>
       </c>
       <c r="E69">
-        <v>-28.12587864857739</v>
+        <v>-26.05005333430534</v>
       </c>
       <c r="F69">
-        <v>-2.732543154168862</v>
+        <v>-2.424229777051303</v>
       </c>
       <c r="G69">
-        <v>-15.98623491543526</v>
+        <v>-15.7279147022787</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.722638127390578</v>
       </c>
       <c r="E70">
-        <v>-27.83791298642963</v>
+        <v>-26.74766475518696</v>
       </c>
       <c r="F70">
-        <v>-2.795697056590894</v>
+        <v>-2.421857332809685</v>
       </c>
       <c r="G70">
-        <v>-16.26332757707226</v>
+        <v>-15.04219809418392</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.725254194651658</v>
       </c>
       <c r="E71">
-        <v>-27.87678993578548</v>
+        <v>-25.5862787257578</v>
       </c>
       <c r="F71">
-        <v>-2.956625648667559</v>
+        <v>-2.682252969144904</v>
       </c>
       <c r="G71">
-        <v>-15.95923079547143</v>
+        <v>-15.09404620314722</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.697572422375455</v>
       </c>
       <c r="E72">
-        <v>-27.84239164722321</v>
+        <v>-25.67070306668279</v>
       </c>
       <c r="F72">
-        <v>-3.017100610908937</v>
+        <v>-2.73738330490342</v>
       </c>
       <c r="G72">
-        <v>-15.91347409030039</v>
+        <v>-14.97342813169664</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.638512080986686</v>
       </c>
       <c r="E73">
-        <v>-27.66798652776581</v>
+        <v>-25.93434629493536</v>
       </c>
       <c r="F73">
-        <v>-3.023986829128409</v>
+        <v>-2.600020937068997</v>
       </c>
       <c r="G73">
-        <v>-15.96147203480151</v>
+        <v>-15.14026803996652</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.551438412950498</v>
       </c>
       <c r="E74">
-        <v>-28.35652288673605</v>
+        <v>-26.17697287531832</v>
       </c>
       <c r="F74">
-        <v>-3.11367665293172</v>
+        <v>-2.9864642708838</v>
       </c>
       <c r="G74">
-        <v>-15.7041797460349</v>
+        <v>-15.17293153752974</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.435705210147725</v>
       </c>
       <c r="E75">
-        <v>-28.06891950250891</v>
+        <v>-26.54012931988943</v>
       </c>
       <c r="F75">
-        <v>-3.15382099400619</v>
+        <v>-2.937386815737541</v>
       </c>
       <c r="G75">
-        <v>-15.47468114234323</v>
+        <v>-14.91456001091732</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.290952517482539</v>
       </c>
       <c r="E76">
-        <v>-28.18792779943049</v>
+        <v>-26.53059235362928</v>
       </c>
       <c r="F76">
-        <v>-3.296417815458903</v>
+        <v>-3.109047735884876</v>
       </c>
       <c r="G76">
-        <v>-15.72930678667796</v>
+        <v>-14.59642155041167</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.12174286704351</v>
       </c>
       <c r="E77">
-        <v>-28.07777266919391</v>
+        <v>-27.12265863081413</v>
       </c>
       <c r="F77">
-        <v>-3.297908876783942</v>
+        <v>-2.913816449658284</v>
       </c>
       <c r="G77">
-        <v>-15.81242465353245</v>
+        <v>-14.92791640689551</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.933350907343195</v>
       </c>
       <c r="E78">
-        <v>-28.65114540567509</v>
+        <v>-27.25019404429215</v>
       </c>
       <c r="F78">
-        <v>-3.470557210875414</v>
+        <v>-3.051298930766112</v>
       </c>
       <c r="G78">
-        <v>-15.20322799503238</v>
+        <v>-14.48323730896952</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.72549214722866</v>
       </c>
       <c r="E79">
-        <v>-29.0621225357672</v>
+        <v>-27.41034805604742</v>
       </c>
       <c r="F79">
-        <v>-3.479627005568666</v>
+        <v>-3.184683478332291</v>
       </c>
       <c r="G79">
-        <v>-14.81718859024351</v>
+        <v>-14.51147626241951</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.503621592902762</v>
       </c>
       <c r="E80">
-        <v>-29.50140942111827</v>
+        <v>-27.17882982240527</v>
       </c>
       <c r="F80">
-        <v>-3.51340782825483</v>
+        <v>-3.357038570363173</v>
       </c>
       <c r="G80">
-        <v>-15.2239801497453</v>
+        <v>-14.24084744094794</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.275459169543089</v>
       </c>
       <c r="E81">
-        <v>-29.55834592481671</v>
+        <v>-27.87158671915067</v>
       </c>
       <c r="F81">
-        <v>-3.624550711055842</v>
+        <v>-3.318927042895173</v>
       </c>
       <c r="G81">
-        <v>-14.82558744427664</v>
+        <v>-14.10556365275839</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.044506812214845</v>
       </c>
       <c r="E82">
-        <v>-29.92258467467566</v>
+        <v>-29.01652985945798</v>
       </c>
       <c r="F82">
-        <v>-3.47719574724145</v>
+        <v>-3.447972602005489</v>
       </c>
       <c r="G82">
-        <v>-14.72743142431002</v>
+        <v>-13.9578040737041</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.815330702170487</v>
       </c>
       <c r="E83">
-        <v>-31.02796253757796</v>
+        <v>-29.0736927868568</v>
       </c>
       <c r="F83">
-        <v>-3.604744446454907</v>
+        <v>-3.366370957523112</v>
       </c>
       <c r="G83">
-        <v>-14.50900825071998</v>
+        <v>-13.65225065206599</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.596143013628065</v>
       </c>
       <c r="E84">
-        <v>-31.02678287009896</v>
+        <v>-29.50029768074939</v>
       </c>
       <c r="F84">
-        <v>-3.763735487176424</v>
+        <v>-3.326415484216481</v>
       </c>
       <c r="G84">
-        <v>-14.31011564053888</v>
+        <v>-13.64809922795974</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.394274218919179</v>
       </c>
       <c r="E85">
-        <v>-31.49495689114495</v>
+        <v>-30.12265944904555</v>
       </c>
       <c r="F85">
-        <v>-3.762418383005973</v>
+        <v>-3.391007432449773</v>
       </c>
       <c r="G85">
-        <v>-14.46831502495126</v>
+        <v>-13.48238656044598</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.21105079078269</v>
       </c>
       <c r="E86">
-        <v>-32.33707191761133</v>
+        <v>-30.85676357771798</v>
       </c>
       <c r="F86">
-        <v>-3.89981471390391</v>
+        <v>-3.545719955535831</v>
       </c>
       <c r="G86">
-        <v>-14.27857938373178</v>
+        <v>-13.64475723223785</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.052292580575294</v>
       </c>
       <c r="E87">
-        <v>-33.24319918841314</v>
+        <v>-32.05937909874997</v>
       </c>
       <c r="F87">
-        <v>-3.956898339998227</v>
+        <v>-3.625953965436185</v>
       </c>
       <c r="G87">
-        <v>-14.15257339941604</v>
+        <v>-13.33264396461367</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.925911654840821</v>
       </c>
       <c r="E88">
-        <v>-33.62894592557151</v>
+        <v>-32.57219934503759</v>
       </c>
       <c r="F88">
-        <v>-4.058141403968382</v>
+        <v>-3.72782410353026</v>
       </c>
       <c r="G88">
-        <v>-14.23105153669723</v>
+        <v>-13.39303493634105</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.834188829440032</v>
       </c>
       <c r="E89">
-        <v>-34.9405980437602</v>
+        <v>-33.52667260434529</v>
       </c>
       <c r="F89">
-        <v>-4.094732048884842</v>
+        <v>-3.780437030751667</v>
       </c>
       <c r="G89">
-        <v>-14.51651160218474</v>
+        <v>-13.01177926985643</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.779008227202686</v>
       </c>
       <c r="E90">
-        <v>-35.41931888077006</v>
+        <v>-34.08919738134109</v>
       </c>
       <c r="F90">
-        <v>-4.053505859982316</v>
+        <v>-3.79321459793985</v>
       </c>
       <c r="G90">
-        <v>-14.34377064649111</v>
+        <v>-13.40835283055126</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.763698830386155</v>
       </c>
       <c r="E91">
-        <v>-36.77246314205402</v>
+        <v>-35.39608554487371</v>
       </c>
       <c r="F91">
-        <v>-4.34335658442628</v>
+        <v>-3.849978474216686</v>
       </c>
       <c r="G91">
-        <v>-14.26937772240538</v>
+        <v>-13.35721483360614</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.790463068286179</v>
       </c>
       <c r="E92">
-        <v>-37.83735871156475</v>
+        <v>-37.669243642504</v>
       </c>
       <c r="F92">
-        <v>-4.387413304744172</v>
+        <v>-4.007662351176586</v>
       </c>
       <c r="G92">
-        <v>-14.49593656165817</v>
+        <v>-13.73466999381168</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.854526681163636</v>
       </c>
       <c r="E93">
-        <v>-38.79706688682531</v>
+        <v>-38.14293334489134</v>
       </c>
       <c r="F93">
-        <v>-4.369515598639286</v>
+        <v>-4.069595240046891</v>
       </c>
       <c r="G93">
-        <v>-14.7691625061053</v>
+        <v>-13.6345872363412</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.951857056370007</v>
       </c>
       <c r="E94">
-        <v>-39.85064806402787</v>
+        <v>-39.54198501142806</v>
       </c>
       <c r="F94">
-        <v>-4.332959745153743</v>
+        <v>-4.213557210979417</v>
       </c>
       <c r="G94">
-        <v>-14.71120478534928</v>
+        <v>-13.70997332408872</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.081182778726219</v>
       </c>
       <c r="E95">
-        <v>-41.39451127238188</v>
+        <v>-40.4863326028546</v>
       </c>
       <c r="F95">
-        <v>-4.625581358560072</v>
+        <v>-4.347584571650168</v>
       </c>
       <c r="G95">
-        <v>-14.52899401414056</v>
+        <v>-14.1113471758155</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.233663080096929</v>
       </c>
       <c r="E96">
-        <v>-42.30116611040557</v>
+        <v>-42.79011450596176</v>
       </c>
       <c r="F96">
-        <v>-4.770056917282333</v>
+        <v>-4.644980066398831</v>
       </c>
       <c r="G96">
-        <v>-15.17273621534292</v>
+        <v>-13.73872044627898</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.398411592590268</v>
       </c>
       <c r="E97">
-        <v>-44.66915724646749</v>
+        <v>-43.86699468193379</v>
       </c>
       <c r="F97">
-        <v>-4.972966340965475</v>
+        <v>-4.699445223132898</v>
       </c>
       <c r="G97">
-        <v>-15.3186269914403</v>
+        <v>-13.99890615184692</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.565376819384501</v>
       </c>
       <c r="E98">
-        <v>-45.74816806946013</v>
+        <v>-45.28435723312052</v>
       </c>
       <c r="F98">
-        <v>-4.90086938406282</v>
+        <v>-4.76809700000731</v>
       </c>
       <c r="G98">
-        <v>-15.76612501889297</v>
+        <v>-14.48612575995254</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.724381955116208</v>
       </c>
       <c r="E99">
-        <v>-47.53033995823078</v>
+        <v>-46.72531766236123</v>
       </c>
       <c r="F99">
-        <v>-5.080139687172272</v>
+        <v>-4.651336957847914</v>
       </c>
       <c r="G99">
-        <v>-15.64541094162175</v>
+        <v>-14.80546925903449</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.860088405194898</v>
       </c>
       <c r="E100">
-        <v>-48.85235096071202</v>
+        <v>-48.75944931644466</v>
       </c>
       <c r="F100">
-        <v>-5.153010339229142</v>
+        <v>-5.048739592401754</v>
       </c>
       <c r="G100">
-        <v>-15.92644811826879</v>
+        <v>-15.79865443936185</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.958684116605604</v>
       </c>
       <c r="E101">
-        <v>-50.63579535067883</v>
+        <v>-49.89462680255443</v>
       </c>
       <c r="F101">
-        <v>-5.376030038350048</v>
+        <v>-4.974327348608274</v>
       </c>
       <c r="G101">
-        <v>-16.61710074976263</v>
+        <v>-15.14435987425306</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.01337155854104</v>
       </c>
       <c r="E102">
-        <v>-52.34777815656759</v>
+        <v>-51.99261673285702</v>
       </c>
       <c r="F102">
-        <v>-5.456468654998893</v>
+        <v>-5.179191719362023</v>
       </c>
       <c r="G102">
-        <v>-16.27254248058082</v>
+        <v>-15.38500674004822</v>
       </c>
     </row>
   </sheetData>
